--- a/dollarexpress/resources/sample/dollarexpress/dollarExpressWareHouse.xlsx
+++ b/dollarexpress/resources/sample/dollarexpress/dollarExpressWareHouse.xlsx
@@ -1,29 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\dollarexpress\resources\sample\dollarexpress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3F3092-8181-498D-B7DC-EC02AA55745F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F7D963-FD9D-410B-88C9-C5A978EE656A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DollarExpressWareHouseConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="DollarExpressWareHouse" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -33,7 +25,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{E7AAAF1D-CCE0-47C9-838A-57BB4DC9EF61}">
       <text>
         <r>
           <rPr>
@@ -62,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>sid</t>
   </si>
@@ -70,70 +62,10 @@
     <t>说明</t>
   </si>
   <si>
-    <t>押注_1</t>
-  </si>
-  <si>
-    <t>押注_2</t>
-  </si>
-  <si>
-    <t>押注_3</t>
-  </si>
-  <si>
-    <t>押注_4</t>
-  </si>
-  <si>
-    <t>押注_5</t>
-  </si>
-  <si>
-    <t>押注_6</t>
-  </si>
-  <si>
-    <t>押注_7</t>
-  </si>
-  <si>
-    <t>押注_8</t>
-  </si>
-  <si>
-    <t>押注_9</t>
-  </si>
-  <si>
-    <t>押注_10</t>
-  </si>
-  <si>
     <t>底注倍数</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>stake_1</t>
-  </si>
-  <si>
-    <t>stake_2</t>
-  </si>
-  <si>
-    <t>stake_3</t>
-  </si>
-  <si>
-    <t>stake_4</t>
-  </si>
-  <si>
-    <t>stake_5</t>
-  </si>
-  <si>
-    <t>stake_6</t>
-  </si>
-  <si>
-    <t>stake_7</t>
-  </si>
-  <si>
-    <t>stake_8</t>
-  </si>
-  <si>
-    <t>stake_9</t>
-  </si>
-  <si>
-    <t>stake_10</t>
   </si>
   <si>
     <t>multiplier</t>
@@ -174,6 +106,39 @@
   <si>
     <t>basicWarehouse</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>押分列表</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>betList</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;{,}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认押分</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>defaultBet</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,200,300,400,500,1000,1500,2000,2500,5000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000,2000,3000,4000,5000,10000,15000,20000,25000,50000</t>
+  </si>
+  <si>
+    <t>10000,20000,30000,40000,50000,100000,150000,200000,250000,500000</t>
   </si>
 </sst>
 </file>
@@ -262,7 +227,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -280,6 +245,24 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -768,18 +751,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="15.125" customWidth="1"/>
-    <col min="9" max="9" width="9.375"/>
-    <col min="10" max="11" width="10.375"/>
-    <col min="12" max="12" width="11.5"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="92.5" style="11" customWidth="1"/>
+    <col min="5" max="5" width="13.375" customWidth="1"/>
+    <col min="6" max="6" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -787,282 +768,116 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>50000000</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>500000000</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>5000000000</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>50000000</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ref="E4:E6" si="0">D4*2</f>
-        <v>200</v>
-      </c>
-      <c r="F4">
-        <f t="shared" ref="F4:F6" si="1">D4*3</f>
-        <v>300</v>
-      </c>
-      <c r="G4">
-        <f t="shared" ref="G4:G6" si="2">D4*4</f>
-        <v>400</v>
-      </c>
-      <c r="H4">
-        <f t="shared" ref="H4:M4" si="3">D4*5</f>
-        <v>500</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="3"/>
-        <v>1000</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="3"/>
-        <v>1500</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
-        <v>2000</v>
-      </c>
-      <c r="L4">
-        <f t="shared" si="3"/>
-        <v>2500</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="3"/>
-        <v>5000</v>
-      </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5">
-        <v>500000000</v>
-      </c>
-      <c r="D5">
-        <v>1000</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="1"/>
-        <v>3000</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="2"/>
-        <v>4000</v>
-      </c>
-      <c r="H5">
-        <f t="shared" ref="H5:M5" si="4">D5*5</f>
-        <v>5000</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="4"/>
-        <v>10000</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="4"/>
-        <v>15000</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="4"/>
-        <v>20000</v>
-      </c>
-      <c r="L5">
-        <f t="shared" si="4"/>
-        <v>25000</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="4"/>
-        <v>50000</v>
-      </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6">
-        <v>5000000000</v>
-      </c>
-      <c r="D6">
-        <v>10000</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>20000</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="2"/>
-        <v>40000</v>
-      </c>
-      <c r="H6">
-        <f t="shared" ref="H6:M6" si="5">D6*5</f>
-        <v>50000</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="5"/>
-        <v>100000</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="5"/>
-        <v>150000</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="5"/>
-        <v>200000</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="5"/>
-        <v>250000</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="5"/>
-        <v>500000</v>
-      </c>
-      <c r="N6">
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
         <v>100</v>
       </c>
     </row>
